--- a/tables/Parameters/Radius.xlsx
+++ b/tables/Parameters/Radius.xlsx
@@ -535,17 +535,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>35.5940073597207</t>
+          <t>29.8247550772236</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>4.28924993559849</t>
+          <t>3.59402714904720</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>4.62823618030184</t>
+          <t>3.87806883113850</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -667,17 +667,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>29.2219136230177</t>
+          <t>24.4179192218864</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>3.34603567974393</t>
+          <t>2.79595751310347</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>3.34603567974393</t>
+          <t>2.79595751310347</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -711,17 +711,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>51.0590129277988</t>
+          <t>40.7448210535303</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>5.36624093989413</t>
+          <t>4.28223176063543</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>5.42948536137474</t>
+          <t>4.33270047297629</t>
         </is>
       </c>
       <c r="G7" t="n">
